--- a/光伏配储项目/电价数据/2026/澄海站.xlsx
+++ b/光伏配储项目/电价数据/2026/澄海站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.32119</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.6156</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.3445</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.36351</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.33895</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.32703</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.32703</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.32503</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.32212</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.32413</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.32302</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.31869</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.31943</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.31904</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.32235</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.32508</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.32602</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.32602</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.32603</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.31809</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30843</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.32524</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.34335</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.33746</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.33221</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.28419</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.29857</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.34759</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.32395</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.29754</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.33648</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.35249</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.3122200000000001</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.07518000000000001</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.7183999999999999</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.58702</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.17293</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.26894</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.25421</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.2588</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.24349</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.6106</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.44225</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.31188</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.33502</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.31507</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.34517</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.6172000000000001</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.7563500000000001</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.97522</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.40559</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.9429</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.44927</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.4596</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.71348</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.94226</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.6079600000000001</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.00935</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.21687</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.06502</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.06935</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.248</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.39893</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.46048</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.75327</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.7978500000000001</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.90174</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.75183</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.71048</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.8027300000000001</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.67979</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.43122</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.36676</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40242</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.36981</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.37542</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.59842</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0.66918</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.80563</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.64547</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.45978</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.35352</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.35403</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.34632</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.34135</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.32476</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.31627</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.32194</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.32177</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.31731</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.31835</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.31736</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.3236</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.3814</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.32715</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.32914</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.32596</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.32273</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.35699</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.5194800000000001</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.33933</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.36687</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.38268</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.31043</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30951</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.36832</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.5845199999999999</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.5744400000000001</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.66639</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.62751</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.96968</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.30127</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.35719</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.33368</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.31002</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.32756</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.81576</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.80899</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.55768</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.45262</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.39882</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.41725</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.46004</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.76644</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.40058</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.38751</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.64422</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.69463</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.59911</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.32232</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.59115</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.70872</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.71048</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.86856</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.73526</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.7102999999999999</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.841</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.86619</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.02765</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.8256699999999999</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.06809999999999999</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.80065</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.85489</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.82643</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.7864800000000001</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.8254</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.8646</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.74361</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.5004</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.8566</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.86826</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.49615</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.46715</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.48905</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.32237</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.35513</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.3413</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.32749</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.42872</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.41582</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.39261</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.32017</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.34866</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.34202</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.30756</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.33688</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.32747</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.32281</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.33668</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.31675</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.32506</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.32573</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.31683</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.32108</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.31768</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.31872</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.31631</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.31383</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.31742</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.32368</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.33228</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.38229</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.34864</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.33297</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.35286</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.33432</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36719</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.35493</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.17321</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.20928</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.28666</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.36765</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.38724</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.13434</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.96724</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.7781</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.38599</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.7666000000000001</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.7864800000000001</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.7849400000000001</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.7907799999999999</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.7921900000000001</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.7836000000000001</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.79826</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.8172999999999999</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.16013</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.63575</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.72657</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.8136100000000001</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.8118500000000001</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.81008</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.7974600000000001</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.59309</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.7877999999999999</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.61403</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.43087</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45805</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.51376</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.47433</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.3372</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.55445</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.57613</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.83694</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.72472</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.70248</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.46115</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.4609</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.67644</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.9156799999999999</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.81062</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.5859</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.48658</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.61942</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.50219</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.49236</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.46786</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.60184</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.4838</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.88613</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.8685700000000001</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.66776</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.58749</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.73976</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.47251</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.50044</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.42077</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.33646</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.33445</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.39982</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.38726</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.3615</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.34338</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.34464</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.3425</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.33208</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.32808</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.3392</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.33946</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.35759</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.32889</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.32331</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.32685</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.32683</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.32027</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.31831</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.31147</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.32567</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33815</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.34411</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.3412</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.32968</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.41894</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.43932</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.46141</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35734</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.44262</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34584</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.37431</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.3518</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.53655</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.35323</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.35347</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.37064</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.7173099999999999</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.48008</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.4647</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.37548</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.40203</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.29064</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.76495</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.48509</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.44977</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.32792</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.5164099999999999</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.77734</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.31946</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34519</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.6471</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.49947</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.46039</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.65573</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.37531</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.40654</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.31877</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.35157</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.60393</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.62029</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45065</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.54935</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.42537</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.58694</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.6873899999999999</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.76001</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.6180099999999999</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.66391</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.65779</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.63049</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.5024999999999999</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.5430199999999999</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.5096499999999999</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.49682</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.48302</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.40031</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.41917</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.36398</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.32527</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.31369</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.30755</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.3054</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.30471</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.44511</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.36569</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.36531</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.36664</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35393</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34015</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32788</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32761</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31581</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31823</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31681</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31193</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31331</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31816</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.3157799999999999</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30994</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.3093399999999999</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31452</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31968</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.30764</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.32023</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.34409</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.3001</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.31872</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.3136</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.33659</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.28905</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.29983</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.31928</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14336</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.31723</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.02404</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.30601</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.30014</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.29909</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.32412</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.31643</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.40783</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.46214</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.26674</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.25727</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.24108</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.10615</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.31888</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.28183</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.02931</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26344</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29978</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30052</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30478</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.34522</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.33663</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34738</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.34668</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.36085</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.36485</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.41717</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.36621</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.36102</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.42323</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34191</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35134</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34273</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.34925</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.31693</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.47343</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.32733</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.29944</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.23908</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.24568</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.29772</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.42562</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.28719</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.32717</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.19026</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.39701</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.22337</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.24784</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.31697</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.40836</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.30479</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.22497</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.24752</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.21384</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.19158</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.38464</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.17286</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.30509</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.24838</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.26989</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.2667</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.08877</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.03501</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04482999999999999</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.32137</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.00996</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.2061</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04921</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27525</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.19384</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.32822</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.009220000000000001</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.06024</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05845</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.35436</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34545</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.34667</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.3156</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.30184</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.56097</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31293</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.37574</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.32913</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31928</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31462</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28102</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.44645</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.40148</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.46288</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.5149</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.5195700000000001</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86287</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88748</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63159</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18707</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8703099999999999</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.65328</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33083</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0329</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7909700000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.57201</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7775299999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39987</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20698</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62183</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.42267</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.40896</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.32789</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39271</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.35328</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.37781</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.38725</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.39792</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.32359</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.37435</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.32745</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.32546</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.3202</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.32185</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.31429</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44361</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.36333</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.47314</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.32054</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.61765</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.65732</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>1.00099</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.56816</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.28813</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.43823</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.45359</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.7686499999999999</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.36132</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.00472</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87501</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.32781</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.31797</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.30082</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.31638</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29173</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.26552</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.42601</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.78298</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.62787</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.36982</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.34472</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32114</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.32487</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31892</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.30379</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.28476</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31525</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29313</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.3077</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.29452</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30527</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.17777</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.26183</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.2614</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.27626</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.26074</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.2805</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.32402</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.29123</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.30995</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.30785</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.30014</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.29331</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.30105</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.30129</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.30602</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.30102</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.30368</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.28916</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.32317</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.81986</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.30712</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.30803</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.31783</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.30315</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.30365</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.2971</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.3003</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.30068</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.30082</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.30663</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.30929</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.29257</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.29921</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.29927</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.29591</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.30926</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.3146</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.29441</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.29714</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.29723</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.29706</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.29651</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.29642</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.29902</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.32915</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.33861</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.29169</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.29558</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.32873</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.30682</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30332</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30338</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.3736</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31204</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.50656</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.38452</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.3989</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30417</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.33178</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.3805</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.60136</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.45457</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.50771</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.37986</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.25188</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.4186</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.36757</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.39711</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.41231</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.56396</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.56441</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.45912</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.43108</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.50447</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.49055</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.45408</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.6520499999999999</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.53727</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.49776</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.54069</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.5376299999999999</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.35703</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.40452</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.34079</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.39967</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.38044</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.40271</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.36846</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.38789</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.39629</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.39232</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.37198</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.39987</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.40677</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.41848</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.41477</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.38742</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.37783</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.34045</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.55506</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.43018</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.5944299999999999</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.3419700000000001</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.37688</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.33743</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.33746</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.33918</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.36505</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.1852</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0.4343</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7977300000000001</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.39227</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.70443</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.36432</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.35634</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.36518</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.36739</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.21352</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.24372</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.31255</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.30877</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.30378</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.33341</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.34241</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.30851</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.24682</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38379</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.3088</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.34396</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.28583</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.31315</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.34718</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.38296</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.31302</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.33387</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.35141</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.31405</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.58261</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.33273</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.25332</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.39363</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.38514</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.32176</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.31244</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.31557</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.48393</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.32774</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.47922</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.39611</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.3088</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.18764</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.3018</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.04013000000000001</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.4302</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30068</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.34299</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.37238</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.3464100000000001</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.33409</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.38105</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.37125</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.32814</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.37305</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32919</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.4724</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31593</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.43668</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.38965</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.4064700000000001</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.4023</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.39861</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.40516</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.38393</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33627</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.40487</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.38271</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.34717</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.38446</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.3436</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.39049</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.4612</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.35784</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.35213</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.34184</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.31647</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.30472</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.33166</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.33186</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.31208</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.31336</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34167</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.31296</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.35559</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.34131</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.32526</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.32895</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.22972</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.30447</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.2355</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.18545</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.23176</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.18269</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.19706</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.29694</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32259</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32008</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.36944</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.36456</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.26353</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.25603</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.41574</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.43693</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.35883</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.04504</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.31518</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.18487</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.04797</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.30374</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.29113</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.23113</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.38641</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.20432</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31161</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.22572</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.42237</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.23921</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.29263</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.31079</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.34432</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.29293</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.30601</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.35438</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.31393</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.33975</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.30516</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.2834</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.31126</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.27146</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.29533</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.30356</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.26988</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.29545</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.31118</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.28436</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.30022</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.29678</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.2967</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.29318</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.29574</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.29399</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.29431</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.30084</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.2802</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.28055</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.29847</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.30233</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.30342</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.30487</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.29149</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.30662</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.3086</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.30708</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.30676</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.30678</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.3055</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.30496</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.30663</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.30679</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.30522</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.40059</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.43066</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.41287</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39536</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.38598</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.28338</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.28575</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.24799</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.28045</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.28883</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.30654</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.35069</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.30547</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.30471</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.30389</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.29782</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.29985</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.30071</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.30286</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.34265</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.30565</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.30311</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.30475</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.30278</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.29693</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.29525</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.29495</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.29876</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.2947</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.29364</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.29509</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.29364</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.29978</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.29912</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.29475</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.29983</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.29926</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.30063</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.29033</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.30082</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.29424</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.30967</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.3074</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28205</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.3012</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31697</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30299</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28476</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.31125</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.28394</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.38824</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.30172</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.28678</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.29827</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.29321</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.2796</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30035</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.29983</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31573</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.30257</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30999</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29422</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.31266</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24415</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.29429</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.28678</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.30343</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.28861</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28799</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.29292</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.32571</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.3174</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.30893</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.38018</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.31746</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.31714</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36126</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.31742</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.36943</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.43801</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.29669</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.35837</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.33446</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.32346</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.31385</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.31085</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.35614</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.31615</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.31576</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.31482</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.32243</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.28739</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.30692</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.30734</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.30297</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.30331</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.30762</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.29661</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.33695</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.30365</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.2871</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.2924</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.28611</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.29182</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.29324</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.29714</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.29902</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.31657</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.29382</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.29507</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.31279</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.30825</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.29301</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.30956</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.30507</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.29565</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.29542</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.28866</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.31294</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.29516</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.4008</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.05097</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.41424</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.64951</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.38773</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.4849</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.48863</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.37912</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.43443</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.49238</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.38542</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.42741</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.38974</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.54648</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.27702</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.30657</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.47189</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.2901</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.35786</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.5003299999999999</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.83739</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.67014</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.5353300000000001</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.43558</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.41438</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.3997</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.5348200000000001</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.41626</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.46711</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.41405</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.3697</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.41454</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.36716</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.53615</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.53018</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.33339</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.62673</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.36128</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.34413</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.85521</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.42946</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.42455</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.59415</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.5679299999999999</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.6725599999999999</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.37331</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.30893</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.35701</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.45527</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.34429</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.45126</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.30465</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.54532</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.42849</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.40161</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.28446</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.34758</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.32625</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.30488</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.38409</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.29424</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.28086</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.28152</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.19746</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.18975</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.27933</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.27654</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.27393</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.27922</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.27935</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.27358</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.19154</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.29506</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.1889</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.15235</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.23453</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.2898</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.29298</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.26169</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.18863</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.19436</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.35594</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.20105</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.16528</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.15675</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.2482</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.25991</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32488</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.32564</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.3829</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.44492</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33288</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.39147</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.33716</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32574</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33748</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34374</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.30662</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.33699</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.26903</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.34486</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.29611</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.33494</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.33242</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.34707</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.32768</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.33979</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.39387</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.4316</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.33852</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.44436</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.47783</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.35622</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.3445299999999999</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34231</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.34552</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.32175</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.32571</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.2993</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.26201</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.28625</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.27888</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.31599</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.29634</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.33636</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.32827</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.27311</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.32818</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.28836</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.35798</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.25795</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35408</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.27948</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.35222</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36007</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.27511</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.32151</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.23344</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.32111</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.29209</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.3202</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.32022</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.32116</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.32064</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.28015</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.31605</v>
+      </c>
+      <c r="L131" t="n">
+        <v>-0.01961</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.31683</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.28854</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.28493</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.27312</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.3098399999999999</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.28513</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.28242</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.29418</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.2825</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.3094</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.28305</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.28486</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.27246</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.31484</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.28372</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.28922</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.28872</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.30613</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.27989</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.27364</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.28348</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.29244</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.27351</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.28421</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.27011</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.29105</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.29927</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.30658</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31631</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.30092</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31143</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.30576</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.30615</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.30459</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.3701</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31808</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.3055</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.35667</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32748</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32127</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32275</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.31802</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.30275</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.31971</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.32089</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.32055</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.32397</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.32412</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.32305</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.32943</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.34165</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.32717</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.31502</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.32857</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.32697</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.31854</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.32455</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.32407</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.3967</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.32128</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.58584</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.5197000000000001</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.20328</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.3431</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.32803</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.32017</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.30942</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.2963</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.38096</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.32248</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.33186</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.33184</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.32793</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.31484</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.32879</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.3298</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.3119</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.32594</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.32189</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.3109</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.32962</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.31742</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.28331</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.32859</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.32633</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.30816</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.32638</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.32169</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.32773</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.31787</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.30775</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.40443</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.31565</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.31796</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.31915</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31791</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.31688</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.33341</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.32468</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.31304</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.32683</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.32349</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.32713</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.32272</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.31916</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.32125</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33535</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.33577</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.32581</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.32798</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.32678</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.33014</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33283</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.34851</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.40982</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.37137</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.38832</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.35645</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.34035</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.33292</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.44218</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.49653</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.61493</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.5777100000000001</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.62362</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.32811</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.7661699999999999</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.39932</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.36904</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.47896</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40285</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.43273</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.34251</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.32232</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.31608</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.31579</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.31975</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.34475</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.31627</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.31387</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.32768</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.33914</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.32665</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.34384</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.31941</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.31799</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.31849</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.32022</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.36454</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.33251</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.32695</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.35787</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.30958</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.30875</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.30901</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.3087</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.2864</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.30258</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.30997</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.29399</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.28066</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.29586</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.29346</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.30749</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.30888</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.31113</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.44873</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.40201</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.42204</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.44214</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.47378</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.5129400000000001</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.57585</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.40437</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.31534</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32437</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.33284</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.32572</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.34935</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.45389</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.37919</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.35996</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.32146</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.35209</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.34461</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.41342</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.63427</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.67964</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.39543</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.48323</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.34435</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.36212</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.33884</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33563</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.33628</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.34312</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.5224800000000001</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.36391</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.33756</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.33637</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.36388</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.34092</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.33733</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.34224</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.32554</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.34183</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.44086</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.32264</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.32395</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.33491</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.68184</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.5559299999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6422899999999999</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.33339</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.32445</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.3159</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.31974</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.31472</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.32474</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.32009</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.31711</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.40429</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.39423</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.3146</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.38596</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.31224</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.26467</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.28596</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.2901</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.31134</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.30737</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.31331</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.32682</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.3358</v>
+      </c>
+      <c r="V134" t="n">
+        <v>-0.005759999999999999</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.27486</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.28316</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.32969</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.3358</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.27483</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.28202</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.34935</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.29079</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.33122</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.32499</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.53249</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.31704</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.36037</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.36925</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.32182</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.34772</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.3245</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.33381</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.33323</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.5486799999999999</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.5944400000000001</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.41123</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.6337999999999999</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.5065</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.38152</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.37077</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.41787</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.38163</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.41176</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.41121</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.34731</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.33846</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.31042</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.3428</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.33593</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.34607</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34769</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.35507</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.3542</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.37239</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.36653</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.39336</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.5367000000000001</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.3873</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.37273</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.3779</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.5740499999999999</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.39501</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.39153</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.41998</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.41425</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.40305</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.39881</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.39099</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.34366</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.33157</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.34163</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.2903</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.3952</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.34239</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.32994</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.37915</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.24208</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.32614</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36065</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.36819</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.26509</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.29209</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.23633</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.16501</v>
+      </c>
+      <c r="J135" t="n">
+        <v>-0.0073</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.2751</v>
+      </c>
+      <c r="L135" t="n">
+        <v>-0.01009</v>
+      </c>
+      <c r="M135" t="n">
+        <v>-0.009560000000000001</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.16525</v>
+      </c>
+      <c r="O135" t="n">
+        <v>-0.0212</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.19858</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.32129</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.16404</v>
+      </c>
+      <c r="S135" t="n">
+        <v>-0.01009</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.15473</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.15922</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.19449</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.15688</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.15956</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.16225</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>-0.01061</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.16494</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>-0.01072</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.0361</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.17572</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.18049</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.14729</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.28319</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.03951</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.34906</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.37066</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.36583</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.19416</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.34264</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.37606</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.33687</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.30623</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.32781</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.44201</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>7.000000000000001e-05</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.3892</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.34844</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.2995</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.34981</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.36615</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.35471</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.41737</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.34913</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.35701</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.35086</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.34213</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.39671</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.38483</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.32874</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.36142</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.26985</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.28792</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.36528</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.24937</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.40086</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.37758</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.36475</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.35724</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.37774</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.3717200000000001</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.37057</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.36689</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.37364</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.21775</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.37931</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.29099</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.24405</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.40752</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.35276</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.27515</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.2736</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.23488</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.23948</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.27534</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.22932</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.2619</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.37321</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.22779</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.34894</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.29719</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.28461</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.27221</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.03784000000000001</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.18006</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.26564</v>
+      </c>
+      <c r="L136" t="n">
+        <v>-0.01991</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.20003</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.22124</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.21281</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.02598</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.0317</v>
+      </c>
+      <c r="R136" t="n">
+        <v>-0.01766</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-0.01767</v>
+      </c>
+      <c r="T136" t="n">
+        <v>-0.01802</v>
+      </c>
+      <c r="U136" t="n">
+        <v>-0.01802</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-0.01781</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.19465</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.03195</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>-0.01802</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>-0.01799</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.17326</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.03171</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.03169</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.30409</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>-0.01694</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.01622</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.24396</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.0234</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.007719999999999999</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00038</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.2849</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02206</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0.00236</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04298</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.0409</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04861</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04827</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02936</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04366</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.03531</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.31215</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04908</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.01656</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.08659</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.02656</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.27419</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.30888</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.32394</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.32882</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.34395</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>-0.01707</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.33015</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.34462</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.33311</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.32378</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.28041</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29443</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.3129</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.32148</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.29268</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.34631</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.34891</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.33261</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.34425</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.3313</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.31314</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.30325</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.29143</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.3117200000000001</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29834</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.26778</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.32931</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.31739</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.29718</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.00305</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.27584</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.30142</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.28162</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.27716</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.16607</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.31761</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.16115</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.16547</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.16289</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.04354</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.15901</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.14809</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.04319</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.04412</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.04328</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>-0.01267</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>-0.01123</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>-0.00876</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.41432</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.18955</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.27496</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.32367</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.04382</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.23294</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.30081</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.85724</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.86225</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32906</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.35901</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.09028</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.01717</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.24719</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.28142</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29541</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.2927</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.5263</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.30082</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.29387</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.29313</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00177</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31672</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.31398</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.0692</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.30838</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30269</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.30837</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30826</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25453</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29188</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47528</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32557</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.31446</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.32782</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32195</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.33087</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.6376000000000001</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.50564</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.35807</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.4181</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.74605</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.87591</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37345</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.57762</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.42406</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.74295</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.7476799999999999</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.74591</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.74946</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.83341</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.35826</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.41868</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.36869</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.33232</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.31809</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.34784</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.30667</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.30651</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.32882</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.32899</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.44971</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.30332</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.28825</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.26788</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.3566</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.26197</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.18742</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.25742</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.25208</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.24552</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.21292</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.25355</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.19954</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.16389</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.19517</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.15848</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.16112</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.04411</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.15389</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.17843</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.22905</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.30905</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.27792</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.23843</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.24753</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.25121</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.27447</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.3029</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.35459</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.32118</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.37918</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.29961</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.32738</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32548</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.32987</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.28686</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.30946</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30724</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.31975</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.32095</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30862</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25863</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31132</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30249</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30225</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32049</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31818</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.32526</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31694</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31287</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32797</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32815</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32751</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.32474</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.32525</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.32145</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.3279</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.33471</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.37569</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.34952</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.33498</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33727</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.3385</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.32075</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.39707</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.36233</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.30956</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.32448</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.31627</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.31768</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.3213</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.30621</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.29472</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.28946</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.29026</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.35257</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.34842</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.32984</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32889</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.32951</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32217</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.31778</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.31203</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.31187</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.32575</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.3142200000000001</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.31369</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.32131</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.31199</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.30115</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.29318</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.29923</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.29931</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.30545</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.31099</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.30619</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.31171</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.31185</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.30192</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.31458</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.33184</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.55043</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.31113</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.41805</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.35458</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.31761</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.30783</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.3172</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.32893</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.33554</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.33314</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33235</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.36343</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.33256</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.29596</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32846</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33337</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33297</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33217</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32261</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.32504</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32822</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.33189</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.45073</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.41514</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.20523</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.75249</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.7642899999999999</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.4067</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.42426</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.51625</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.64763</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.79211</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.40915</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.5144299999999999</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.3639</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.34405</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.33818</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.42438</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.3425299999999999</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.33227</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.35459</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.33232</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.33403</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.32769</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.32592</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.33097</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.32668</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.19997</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.31849</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.30671</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.31562</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.31773</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.38662</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.32399</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.32038</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.31509</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.31332</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.31867</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.31176</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.31693</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.31691</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.31386</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.31518</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.31477</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.30433</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.30082</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.30336</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.29875</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.29671</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.29261</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.2921</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.30303</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.30631</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.30176</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.33629</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.31467</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.32891</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.31781</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.36041</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39096</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.34452</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35365</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43458</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37965</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.34207</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.35441</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33497</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.36268</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.34131</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.3524</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.35351</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34251</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.34122</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34216</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34152</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34416</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.33849</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.33753</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.3425299999999999</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37353</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.34989</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.36537</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.35275</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.34835</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.38914</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.37432</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.46958</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.47834</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.90851</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.7392000000000001</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.5106000000000001</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.6287999999999999</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.44715</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.5169900000000001</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.47588</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.40914</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.6049500000000001</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.5746100000000001</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.8501299999999999</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.76046</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.6635700000000001</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.55968</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.33401</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.39764</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.33796</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.32514</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.31877</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.32023</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.28345</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33836</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.30881</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.28274</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.29443</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.28818</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.29831</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.3233</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.28928</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.31245</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.30015</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.04563</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.28709</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.28794</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31872</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.28227</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31376</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.32705</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.28911</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.28015</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35569</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.35636</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.33406</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30378</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30219</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.31264</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.30644</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.32212</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.32596</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.35308</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.35964</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.37485</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.32763</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.26656</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.42723</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.38678</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.5499299999999999</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.34387</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.33814</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.19883</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.39523</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.29756</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.31349</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.43473</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.5190399999999999</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.33381</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.34267</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.30822</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.35412</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.38098</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.32132</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.34496</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.34966</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.34487</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.33978</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.34334</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.34432</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.47045</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.46511</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.33535</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35606</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.38375</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.6385</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.34424</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.6154400000000001</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.67596</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.5250900000000001</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.41615</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.38775</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.4303</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.50606</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.38017</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.44121</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.39422</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.40533</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.36214</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.35902</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.3479100000000001</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.3078</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.32416</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34292</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.6667799999999999</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.3949</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.43912</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.41695</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.40765</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33757</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.36118</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.34165</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33722</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33837</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.33826</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.33566</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.33345</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.33783</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.33837</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.32808</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.33193</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.33394</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.32571</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.33944</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33497</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.32537</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.32825</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.33867</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33455</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.35643</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.35547</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.33312</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.33577</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.31551</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.32157</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.30921</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.38376</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.31891</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.30309</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.27712</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.3894</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.45278</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.30419</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32421</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35118</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32328</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35384</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35465</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.34486</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.36535</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.37457</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.73863</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.76554</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.53991</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.63486</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.81759</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.41448</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.36568</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.41249</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.38699</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.41562</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.54144</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.56814</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.39395</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.40069</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39046</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.38543</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.41457</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.47568</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.40638</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.3672</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.43227</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.39735</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.39326</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.34242</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.33554</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.33698</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.33809</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.33772</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34843</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.2664</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.36702</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.30612</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37213</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.3581</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35573</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.34148</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.3420299999999999</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.3386</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.34215</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.33534</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.3469</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.31719</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35531</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33656</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.32742</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32915</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.33519</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.33472</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.33197</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.32863</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.30519</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.3186</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17611</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29576</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31176</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14577</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19867</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14654</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.2874</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04787</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12174</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33388</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22624</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26017</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14354</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.1455</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28358</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.18772</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22686</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.37221</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.22427</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.37534</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30883</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.2422</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.37078</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.34931</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.25928</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.21232</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.34468</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.41081</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.42024</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.37467</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.42251</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.69731</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.7954199999999999</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.55502</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>1.30967</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.60634</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.6723300000000001</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.46077</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.44901</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.51789</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.43078</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.36419</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.75787</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.6181</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.76837</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>1.16685</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.81351</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.43837</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.74405</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.43848</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.7100700000000001</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.74056</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.6256499999999999</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.45584</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.44733</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.40046</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.43027</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.3906</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.37575</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.36868</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.36767</v>
       </c>
     </row>
   </sheetData>
